--- a/backend/data/financials_by_company/0KN.F.xlsx
+++ b/backend/data/financials_by_company/0KN.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,552 +662,612 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-4914000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="D2" t="n">
-        <v>230300000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-21000000</v>
+        <v>1400000</v>
       </c>
       <c r="F2" t="n">
-        <v>-21000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33600000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4016300000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>209300000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>175700000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>9900000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>18200000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>147786000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4366400000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>162000000</v>
-      </c>
+        <v>1400000</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>48500000</v>
+        <v>47900000</v>
       </c>
       <c r="T2" t="n">
-        <v>46800000</v>
+        <v>46100000</v>
       </c>
       <c r="U2" t="n">
-        <v>2.715</v>
+        <v>2.044</v>
       </c>
       <c r="V2" t="n">
-        <v>2.814</v>
-      </c>
-      <c r="W2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="Y2" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-1400000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="AP2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>40200000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>171900000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-21000000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>9900000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18200000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>179800000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>350100000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>360000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>360000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>529900000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4016300000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4546200000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4546200000</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-509798.471161</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.182071</v>
+        <v>0.286049</v>
       </c>
       <c r="D3" t="n">
-        <v>178900000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-2800000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-2800000</v>
-      </c>
+        <v>113300000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="H3" t="n">
-        <v>29700000</v>
+        <v>24900000</v>
       </c>
       <c r="I3" t="n">
-        <v>3670100000</v>
+        <v>3241300000</v>
       </c>
       <c r="J3" t="n">
-        <v>176100000</v>
+        <v>113300000</v>
       </c>
       <c r="K3" t="n">
-        <v>146400000</v>
+        <v>88400000</v>
       </c>
       <c r="L3" t="n">
-        <v>3300000</v>
+        <v>-3000000</v>
       </c>
       <c r="M3" t="n">
-        <v>2500000</v>
+        <v>3100000</v>
       </c>
       <c r="N3" t="n">
-        <v>10800000</v>
+        <v>2300000</v>
       </c>
       <c r="O3" t="n">
-        <v>119990201.528839</v>
+        <v>60900000</v>
       </c>
       <c r="P3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="Q3" t="n">
-        <v>3992500000</v>
+        <v>3528400000</v>
       </c>
       <c r="R3" t="n">
-        <v>140600000</v>
+        <v>88300000</v>
       </c>
       <c r="S3" t="n">
-        <v>47000000</v>
+        <v>46700000</v>
       </c>
       <c r="T3" t="n">
-        <v>46300000</v>
+        <v>45900000</v>
       </c>
       <c r="U3" t="n">
-        <v>2.504</v>
+        <v>1.304</v>
       </c>
       <c r="V3" t="n">
-        <v>2.542</v>
+        <v>1.327</v>
       </c>
       <c r="W3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="X3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="AA3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="AB3" t="n">
-        <v>117700000</v>
+        <v>60900000</v>
       </c>
       <c r="AC3" t="n">
-        <v>26200000</v>
+        <v>24400000</v>
       </c>
       <c r="AD3" t="n">
-        <v>143900000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-2800000</v>
-      </c>
+        <v>85300000</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>2800000</v>
-      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>3300000</v>
+        <v>-3000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5000000</v>
+        <v>2200000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2500000</v>
+        <v>3100000</v>
       </c>
       <c r="AK3" t="n">
-        <v>10800000</v>
+        <v>2300000</v>
       </c>
       <c r="AL3" t="n">
-        <v>125200000</v>
+        <v>83800000</v>
       </c>
       <c r="AM3" t="n">
-        <v>322400000</v>
+        <v>287100000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>324000000</v>
+        <v>287600000</v>
       </c>
       <c r="AR3" t="n">
-        <v>324000000</v>
+        <v>287600000</v>
       </c>
       <c r="AS3" t="n">
-        <v>447600000</v>
+        <v>370900000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3670100000</v>
+        <v>3241300000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4117700000</v>
+        <v>3612200000</v>
       </c>
       <c r="AV3" t="n">
-        <v>4117700000</v>
+        <v>3612200000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-509798.471161</v>
       </c>
       <c r="C4" t="n">
-        <v>0.286049</v>
+        <v>0.182071</v>
       </c>
       <c r="D4" t="n">
-        <v>113300000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>178900000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2800000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2800000</v>
+      </c>
       <c r="G4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="H4" t="n">
-        <v>24900000</v>
+        <v>29700000</v>
       </c>
       <c r="I4" t="n">
-        <v>3241300000</v>
+        <v>3670100000</v>
       </c>
       <c r="J4" t="n">
-        <v>113300000</v>
+        <v>176100000</v>
       </c>
       <c r="K4" t="n">
-        <v>88400000</v>
+        <v>146400000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3000000</v>
+        <v>3300000</v>
       </c>
       <c r="M4" t="n">
-        <v>3100000</v>
+        <v>2500000</v>
       </c>
       <c r="N4" t="n">
-        <v>2300000</v>
+        <v>10800000</v>
       </c>
       <c r="O4" t="n">
-        <v>60900000</v>
+        <v>119990201.528839</v>
       </c>
       <c r="P4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3528400000</v>
+        <v>3992500000</v>
       </c>
       <c r="R4" t="n">
-        <v>88300000</v>
+        <v>140600000</v>
       </c>
       <c r="S4" t="n">
-        <v>46700000</v>
+        <v>47000000</v>
       </c>
       <c r="T4" t="n">
-        <v>45900000</v>
+        <v>46300000</v>
       </c>
       <c r="U4" t="n">
-        <v>1.304</v>
+        <v>2.504</v>
       </c>
       <c r="V4" t="n">
-        <v>1.327</v>
+        <v>2.542</v>
       </c>
       <c r="W4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="X4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="AA4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="AB4" t="n">
-        <v>60900000</v>
+        <v>117700000</v>
       </c>
       <c r="AC4" t="n">
-        <v>24400000</v>
+        <v>26200000</v>
       </c>
       <c r="AD4" t="n">
-        <v>85300000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>143900000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-2800000</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>2800000</v>
+      </c>
       <c r="AH4" t="n">
-        <v>-3000000</v>
+        <v>3300000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2200000</v>
+        <v>5000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3100000</v>
+        <v>2500000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2300000</v>
+        <v>10800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>83800000</v>
+        <v>125200000</v>
       </c>
       <c r="AM4" t="n">
-        <v>287100000</v>
+        <v>322400000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>287600000</v>
+        <v>324000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>287600000</v>
+        <v>324000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>370900000</v>
+        <v>447600000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3241300000</v>
+        <v>3670100000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3612200000</v>
+        <v>4117700000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3612200000</v>
+        <v>4117700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-4910994.764398</v>
       </c>
       <c r="C5" t="n">
-        <v>0.224247</v>
+        <v>0.233857</v>
       </c>
       <c r="D5" t="n">
-        <v>149900000</v>
+        <v>230300000</v>
       </c>
       <c r="E5" t="n">
-        <v>1400000</v>
+        <v>-21000000</v>
       </c>
       <c r="F5" t="n">
-        <v>1400000</v>
+        <v>-21000000</v>
       </c>
       <c r="G5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="H5" t="n">
-        <v>22000000</v>
+        <v>33600000</v>
       </c>
       <c r="I5" t="n">
-        <v>2830000000</v>
+        <v>4016300000</v>
       </c>
       <c r="J5" t="n">
-        <v>149900000</v>
+        <v>209300000</v>
       </c>
       <c r="K5" t="n">
-        <v>127900000</v>
+        <v>175700000</v>
       </c>
       <c r="L5" t="n">
-        <v>-3600000</v>
+        <v>9900000</v>
       </c>
       <c r="M5" t="n">
-        <v>1700000</v>
+        <v>3800000</v>
       </c>
       <c r="N5" t="n">
-        <v>600000</v>
+        <v>18200000</v>
       </c>
       <c r="O5" t="n">
-        <v>97900000</v>
+        <v>147789005.235602</v>
       </c>
       <c r="P5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3088400000</v>
+        <v>4366400000</v>
       </c>
       <c r="R5" t="n">
-        <v>129800000</v>
+        <v>162000000</v>
       </c>
       <c r="S5" t="n">
-        <v>47900000</v>
+        <v>48500000</v>
       </c>
       <c r="T5" t="n">
-        <v>46100000</v>
+        <v>46800000</v>
       </c>
       <c r="U5" t="n">
-        <v>2.044</v>
+        <v>2.715</v>
       </c>
       <c r="V5" t="n">
-        <v>2.124</v>
+        <v>2.814</v>
       </c>
       <c r="W5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="X5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="AA5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="AB5" t="n">
-        <v>97900000</v>
+        <v>131700000</v>
       </c>
       <c r="AC5" t="n">
-        <v>28300000</v>
+        <v>40200000</v>
       </c>
       <c r="AD5" t="n">
-        <v>126200000</v>
+        <v>171900000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-1400000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-21000000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>21000000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-3600000</v>
+        <v>9900000</v>
       </c>
       <c r="AI5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>18200000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>179800000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>350100000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>360000000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>360000000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>529900000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4016300000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4546200000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4546200000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-613675.5823989999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="D6" t="n">
+        <v>274700000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2500000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2500000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36200000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4406600000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>272200000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>236000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>176786324.417601</v>
+      </c>
+      <c r="P6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4792400000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>224900000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>174900000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>56900000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>231800000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-2500000</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
         <v>2500000</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>600000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>124400000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>258400000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>259800000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>259800000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>382800000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2830000000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3212800000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3212800000</v>
+      <c r="AH6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>226200000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>385800000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>391300000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>391300000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>612000000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4406600000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5018600000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5018600000</v>
       </c>
     </row>
   </sheetData>
@@ -1221,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK5"/>
+  <dimension ref="A1:BM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1535,240 +1595,140 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1241722</v>
-      </c>
-      <c r="C2" t="n">
-        <v>46762699</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48004421</v>
-      </c>
-      <c r="E2" t="n">
-        <v>118500000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>429100000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>699000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>304700000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>429100000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>66700000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>647200000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>647200000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>647200000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>647200000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>578200000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>65700000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1483400000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>83200000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>44100000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>44100000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>20400000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1400200000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>74400000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22600000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>85100000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>393400000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>43000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>139300000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>211100000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2130600000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>425700000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>111900000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>111900000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>218100000</v>
-      </c>
-      <c r="AQ2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
         <v>400000</v>
       </c>
-      <c r="AR2" t="n">
-        <v>217700000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>95100000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-97600000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>192700000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>71500000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>65300000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>55900000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1704900000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>16100000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>476000000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>476000000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>292500000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6600000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>369500000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>370800000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>544200000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>544200000</v>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>62100000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1124215</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>46233511</v>
+        <v>47350604</v>
       </c>
       <c r="D3" t="n">
-        <v>47357726</v>
+        <v>47350604</v>
       </c>
       <c r="E3" t="n">
-        <v>144400000</v>
+        <v>134000000</v>
       </c>
       <c r="F3" t="n">
-        <v>349500000</v>
+        <v>275000000</v>
       </c>
       <c r="G3" t="n">
-        <v>648700000</v>
+        <v>573300000</v>
       </c>
       <c r="H3" t="n">
-        <v>257100000</v>
+        <v>222400000</v>
       </c>
       <c r="I3" t="n">
-        <v>349500000</v>
+        <v>275000000</v>
       </c>
       <c r="J3" t="n">
-        <v>63800000</v>
+        <v>56900000</v>
       </c>
       <c r="K3" t="n">
-        <v>568100000</v>
+        <v>496200000</v>
       </c>
       <c r="L3" t="n">
-        <v>568100000</v>
+        <v>496200000</v>
       </c>
       <c r="M3" t="n">
-        <v>568100000</v>
+        <v>496200000</v>
       </c>
       <c r="N3" t="n">
-        <v>568100000</v>
+        <v>496200000</v>
       </c>
       <c r="O3" t="n">
-        <v>508400000</v>
+        <v>436800000</v>
       </c>
       <c r="P3" t="n">
-        <v>56000000</v>
+        <v>55900000</v>
       </c>
       <c r="Q3" t="n">
         <v>2400000</v>
@@ -1777,187 +1737,191 @@
         <v>2400000</v>
       </c>
       <c r="S3" t="n">
-        <v>1462100000</v>
+        <v>1298200000</v>
       </c>
       <c r="T3" t="n">
-        <v>101000000</v>
+        <v>107000000</v>
       </c>
       <c r="U3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>37300000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>40900000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>40900000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>28200000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>44700000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>44700000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>19400000</v>
+        <v>21800000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1361100000</v>
+        <v>1191200000</v>
       </c>
       <c r="AC3" t="n">
-        <v>99700000</v>
+        <v>93100000</v>
       </c>
       <c r="AD3" t="n">
-        <v>19100000</v>
+        <v>16000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>80600000</v>
+        <v>77100000</v>
       </c>
       <c r="AF3" t="n">
-        <v>76700000</v>
+        <v>55100000</v>
       </c>
       <c r="AG3" t="n">
-        <v>381200000</v>
+        <v>325300000</v>
       </c>
       <c r="AH3" t="n">
-        <v>34300000</v>
+        <v>47300000</v>
       </c>
       <c r="AI3" t="n">
-        <v>144700000</v>
+        <v>112600000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>202200000</v>
+        <v>165400000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2030200000</v>
+        <v>1794400000</v>
       </c>
       <c r="AL3" t="n">
-        <v>412000000</v>
+        <v>380800000</v>
       </c>
       <c r="AM3" t="n">
-        <v>106600000</v>
+        <v>84000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>106600000</v>
+        <v>84000000</v>
       </c>
       <c r="AO3" t="n">
         <v>800000</v>
       </c>
       <c r="AP3" t="n">
-        <v>218600000</v>
+        <v>221200000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>900000</v>
+        <v>3500000</v>
       </c>
       <c r="AR3" t="n">
         <v>217700000</v>
       </c>
       <c r="AS3" t="n">
-        <v>86000000</v>
+        <v>74800000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-85300000</v>
+        <v>-75500000</v>
       </c>
       <c r="AU3" t="n">
-        <v>171300000</v>
+        <v>150300000</v>
       </c>
       <c r="AV3" t="n">
-        <v>57700000</v>
+        <v>38200000</v>
       </c>
       <c r="AW3" t="n">
-        <v>59300000</v>
+        <v>53200000</v>
       </c>
       <c r="AX3" t="n">
-        <v>54300000</v>
+        <v>58900000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1618200000</v>
+        <v>1413600000</v>
       </c>
       <c r="BA3" t="n">
-        <v>13900000</v>
+        <v>11100000</v>
       </c>
       <c r="BB3" t="n">
-        <v>17800000</v>
+        <v>13000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>344700000</v>
+        <v>333900000</v>
       </c>
       <c r="BD3" t="n">
-        <v>344700000</v>
+        <v>333900000</v>
       </c>
       <c r="BE3" t="n">
-        <v>344700000</v>
+        <v>345000000</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>369700000</v>
+        <v>290000000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-1500000</v>
+        <v>-2500000</v>
       </c>
       <c r="BI3" t="n">
-        <v>371200000</v>
+        <v>292500000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>541300000</v>
+        <v>420600000</v>
       </c>
       <c r="BK3" t="n">
-        <v>541300000</v>
-      </c>
+        <v>420600000</v>
+      </c>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1124215</v>
       </c>
       <c r="C4" t="n">
-        <v>47350604</v>
+        <v>46233511</v>
       </c>
       <c r="D4" t="n">
-        <v>47350604</v>
+        <v>47357726</v>
       </c>
       <c r="E4" t="n">
-        <v>134000000</v>
+        <v>144400000</v>
       </c>
       <c r="F4" t="n">
-        <v>275000000</v>
+        <v>349500000</v>
       </c>
       <c r="G4" t="n">
-        <v>573300000</v>
+        <v>648700000</v>
       </c>
       <c r="H4" t="n">
-        <v>222400000</v>
+        <v>257100000</v>
       </c>
       <c r="I4" t="n">
-        <v>275000000</v>
+        <v>349500000</v>
       </c>
       <c r="J4" t="n">
-        <v>56900000</v>
+        <v>63800000</v>
       </c>
       <c r="K4" t="n">
-        <v>496200000</v>
+        <v>568100000</v>
       </c>
       <c r="L4" t="n">
-        <v>496200000</v>
+        <v>568100000</v>
       </c>
       <c r="M4" t="n">
-        <v>496200000</v>
+        <v>568100000</v>
       </c>
       <c r="N4" t="n">
-        <v>496200000</v>
+        <v>568100000</v>
       </c>
       <c r="O4" t="n">
-        <v>436800000</v>
+        <v>508400000</v>
       </c>
       <c r="P4" t="n">
-        <v>55900000</v>
+        <v>56000000</v>
       </c>
       <c r="Q4" t="n">
         <v>2400000</v>
@@ -1966,330 +1930,521 @@
         <v>2400000</v>
       </c>
       <c r="S4" t="n">
-        <v>1298200000</v>
+        <v>1462100000</v>
       </c>
       <c r="T4" t="n">
-        <v>107000000</v>
+        <v>101000000</v>
       </c>
       <c r="U4" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>37300000</v>
+        <v>28200000</v>
       </c>
       <c r="W4" t="n">
-        <v>6800000</v>
+        <v>8700000</v>
       </c>
       <c r="X4" t="n">
-        <v>40900000</v>
+        <v>44700000</v>
       </c>
       <c r="Y4" t="n">
-        <v>40900000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>44700000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>21800000</v>
+        <v>19400000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1191200000</v>
+        <v>1361100000</v>
       </c>
       <c r="AC4" t="n">
-        <v>93100000</v>
+        <v>99700000</v>
       </c>
       <c r="AD4" t="n">
-        <v>16000000</v>
+        <v>19100000</v>
       </c>
       <c r="AE4" t="n">
-        <v>77100000</v>
+        <v>80600000</v>
       </c>
       <c r="AF4" t="n">
-        <v>55100000</v>
+        <v>76700000</v>
       </c>
       <c r="AG4" t="n">
-        <v>325300000</v>
+        <v>381200000</v>
       </c>
       <c r="AH4" t="n">
-        <v>47300000</v>
+        <v>34300000</v>
       </c>
       <c r="AI4" t="n">
-        <v>112600000</v>
+        <v>144700000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>165400000</v>
+        <v>202200000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1794400000</v>
+        <v>2030200000</v>
       </c>
       <c r="AL4" t="n">
-        <v>380800000</v>
+        <v>412000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>84000000</v>
+        <v>106600000</v>
       </c>
       <c r="AN4" t="n">
-        <v>84000000</v>
+        <v>106600000</v>
       </c>
       <c r="AO4" t="n">
         <v>800000</v>
       </c>
       <c r="AP4" t="n">
-        <v>221200000</v>
+        <v>218600000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3500000</v>
+        <v>900000</v>
       </c>
       <c r="AR4" t="n">
         <v>217700000</v>
       </c>
       <c r="AS4" t="n">
-        <v>74800000</v>
+        <v>86000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-75500000</v>
+        <v>-85300000</v>
       </c>
       <c r="AU4" t="n">
-        <v>150300000</v>
+        <v>171300000</v>
       </c>
       <c r="AV4" t="n">
-        <v>38200000</v>
+        <v>57700000</v>
       </c>
       <c r="AW4" t="n">
-        <v>53200000</v>
+        <v>59300000</v>
       </c>
       <c r="AX4" t="n">
-        <v>58900000</v>
+        <v>54300000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1413600000</v>
+        <v>1618200000</v>
       </c>
       <c r="BA4" t="n">
-        <v>11100000</v>
+        <v>13900000</v>
       </c>
       <c r="BB4" t="n">
-        <v>13000000</v>
+        <v>17800000</v>
       </c>
       <c r="BC4" t="n">
-        <v>333900000</v>
+        <v>344700000</v>
       </c>
       <c r="BD4" t="n">
-        <v>333900000</v>
+        <v>344700000</v>
       </c>
       <c r="BE4" t="n">
-        <v>345000000</v>
+        <v>344700000</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>290000000</v>
+        <v>369700000</v>
       </c>
       <c r="BH4" t="n">
-        <v>-2500000</v>
+        <v>-1500000</v>
       </c>
       <c r="BI4" t="n">
-        <v>292500000</v>
+        <v>371200000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>420600000</v>
+        <v>541300000</v>
       </c>
       <c r="BK4" t="n">
-        <v>420600000</v>
-      </c>
+        <v>541300000</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1241722</v>
       </c>
       <c r="C5" t="n">
-        <v>46374873</v>
+        <v>46762699</v>
       </c>
       <c r="D5" t="n">
-        <v>46374873</v>
+        <v>48004421</v>
       </c>
       <c r="E5" t="n">
-        <v>163400000</v>
+        <v>118500000</v>
       </c>
       <c r="F5" t="n">
-        <v>252300000</v>
+        <v>429100000</v>
       </c>
       <c r="G5" t="n">
-        <v>584800000</v>
+        <v>699000000</v>
       </c>
       <c r="H5" t="n">
-        <v>197300000</v>
+        <v>304700000</v>
       </c>
       <c r="I5" t="n">
-        <v>252300000</v>
+        <v>429100000</v>
       </c>
       <c r="J5" t="n">
-        <v>52800000</v>
+        <v>66700000</v>
       </c>
       <c r="K5" t="n">
-        <v>474200000</v>
+        <v>647200000</v>
       </c>
       <c r="L5" t="n">
-        <v>474600000</v>
+        <v>647200000</v>
       </c>
       <c r="M5" t="n">
-        <v>474200000</v>
+        <v>647200000</v>
       </c>
       <c r="N5" t="n">
-        <v>474200000</v>
+        <v>647200000</v>
       </c>
       <c r="O5" t="n">
-        <v>427100000</v>
+        <v>578200000</v>
       </c>
       <c r="P5" t="n">
-        <v>45800000</v>
+        <v>65700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300000</v>
+        <v>2400000</v>
       </c>
       <c r="R5" t="n">
-        <v>2300000</v>
+        <v>2400000</v>
       </c>
       <c r="S5" t="n">
-        <v>1233400000</v>
+        <v>1483400000</v>
       </c>
       <c r="T5" t="n">
-        <v>106500000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>200000</v>
-      </c>
+        <v>83200000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>32600000</v>
+        <v>16600000</v>
       </c>
       <c r="W5" t="n">
-        <v>10000000</v>
+        <v>2100000</v>
       </c>
       <c r="X5" t="n">
-        <v>39800000</v>
+        <v>44100000</v>
       </c>
       <c r="Y5" t="n">
-        <v>39400000</v>
-      </c>
-      <c r="Z5" t="n">
+        <v>44100000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>20400000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1400200000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>74400000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22600000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>51800000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>85100000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>393400000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>139300000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>211100000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2130600000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>425700000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>111900000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>111900000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>218100000</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>400000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>23900000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1126900000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>123600000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13400000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>110200000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>33400000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>279800000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>14700000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>107500000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>157600000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1707600000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>383400000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>94100000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>94100000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>800000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>221900000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4200000</v>
       </c>
       <c r="AR5" t="n">
         <v>217700000</v>
       </c>
       <c r="AS5" t="n">
-        <v>66600000</v>
+        <v>95100000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-67800000</v>
+        <v>-97600000</v>
       </c>
       <c r="AU5" t="n">
-        <v>134400000</v>
+        <v>192700000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2400000</v>
+        <v>71500000</v>
       </c>
       <c r="AW5" t="n">
-        <v>76600000</v>
+        <v>65300000</v>
       </c>
       <c r="AX5" t="n">
-        <v>55400000</v>
+        <v>55900000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1324200000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>62100000</v>
-      </c>
+        <v>1704900000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>13200000</v>
+        <v>16100000</v>
       </c>
       <c r="BC5" t="n">
-        <v>288500000</v>
+        <v>476000000</v>
       </c>
       <c r="BD5" t="n">
-        <v>288500000</v>
+        <v>476000000</v>
       </c>
       <c r="BE5" t="n">
-        <v>299000000</v>
+        <v>292500000</v>
       </c>
       <c r="BF5" t="n">
-        <v>4700000</v>
+        <v>6600000</v>
       </c>
       <c r="BG5" t="n">
-        <v>250200000</v>
+        <v>369500000</v>
       </c>
       <c r="BH5" t="n">
-        <v>-1200000</v>
+        <v>-1300000</v>
       </c>
       <c r="BI5" t="n">
-        <v>251400000</v>
+        <v>370800000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>468600000</v>
+        <v>544200000</v>
       </c>
       <c r="BK5" t="n">
-        <v>468600000</v>
+        <v>544200000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1377157</v>
+      </c>
+      <c r="C6" t="n">
+        <v>46645805</v>
+      </c>
+      <c r="D6" t="n">
+        <v>48022962</v>
+      </c>
+      <c r="E6" t="n">
+        <v>132900000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>530500000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>808100000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>372800000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>530500000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>73600000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>748800000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>748800000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>748800000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>748800000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>679300000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>65900000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1699500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>81400000</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>48800000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>48800000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1618100000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>84100000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>59300000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>71700000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>449800000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>37800000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>174700000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>237300000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2448300000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>457400000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>132700000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>132700000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>218300000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>217700000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>102200000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-106800000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>209000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>75800000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>75500000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>57700000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1990900000</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>603300000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>603300000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>302000000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>467700000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>468100000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>590500000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>590500000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>6600000</v>
       </c>
     </row>
   </sheetData>
@@ -2303,7 +2458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,538 +2695,589 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>110600000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-47200000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>29200000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-18200000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>492400000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>460700000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31700000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-101800000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1900000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-56100000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-56100000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-18000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-47200000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>29200000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>-16300000</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
         <v>1900000</v>
       </c>
-      <c r="AE2" t="n">
-        <v>-18200000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>128800000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-43900000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-33800000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>29100000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-131300000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>53800000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>33600000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>33100000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>162000000</v>
-      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>181400000</v>
+        <v>42900000</v>
       </c>
       <c r="C3" t="n">
-        <v>-11300000</v>
+        <v>-15700000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>4100000</v>
+        <v>11800000</v>
       </c>
       <c r="G3" t="n">
-        <v>-14600000</v>
+        <v>-11800000</v>
       </c>
       <c r="H3" t="n">
-        <v>460700000</v>
+        <v>354600000</v>
       </c>
       <c r="I3" t="n">
-        <v>354600000</v>
+        <v>358400000</v>
       </c>
       <c r="J3" t="n">
-        <v>106100000</v>
+        <v>-3800000</v>
       </c>
       <c r="K3" t="n">
-        <v>-78900000</v>
+        <v>-66800000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2400000</v>
+        <v>-1800000</v>
       </c>
       <c r="M3" t="n">
-        <v>-48100000</v>
+        <v>-43500000</v>
       </c>
       <c r="N3" t="n">
-        <v>-48100000</v>
+        <v>-43500000</v>
       </c>
       <c r="O3" t="n">
-        <v>-7200000</v>
+        <v>-3900000</v>
       </c>
       <c r="P3" t="n">
-        <v>-11300000</v>
+        <v>-15700000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4100000</v>
+        <v>11800000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+        <v>-400000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-400000</v>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-11000000</v>
+        <v>8300000</v>
       </c>
       <c r="Y3" t="n">
-        <v>10000000</v>
+        <v>1800000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1600000</v>
+        <v>1400000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-300000</v>
+        <v>-1300000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-300000</v>
+        <v>-1300000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-12300000</v>
+        <v>-9900000</v>
       </c>
       <c r="AD3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-10500000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>54700000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-20300000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-64500000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-4300000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>71600000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-45400000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-86400000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-19500000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>24900000</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>2000000</v>
       </c>
-      <c r="AE3" t="n">
-        <v>-14300000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>196000000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-25200000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>43200000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>21600000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>116200000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-10800000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-83800000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>13700000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6600000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>29700000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2900000</v>
-      </c>
       <c r="AR3" t="n">
-        <v>26800000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>400000</v>
-      </c>
+        <v>22900000</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>-100000</v>
+        <v>-500000</v>
       </c>
       <c r="AU3" t="n">
-        <v>140600000</v>
+        <v>88300000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>42900000</v>
+        <v>181400000</v>
       </c>
       <c r="C4" t="n">
-        <v>-15700000</v>
+        <v>-11300000</v>
       </c>
       <c r="D4" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>11800000</v>
+        <v>4100000</v>
       </c>
       <c r="G4" t="n">
-        <v>-11800000</v>
+        <v>-14600000</v>
       </c>
       <c r="H4" t="n">
+        <v>460700000</v>
+      </c>
+      <c r="I4" t="n">
         <v>354600000</v>
       </c>
-      <c r="I4" t="n">
-        <v>358400000</v>
-      </c>
       <c r="J4" t="n">
-        <v>-3800000</v>
+        <v>106100000</v>
       </c>
       <c r="K4" t="n">
-        <v>-66800000</v>
+        <v>-78900000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1800000</v>
+        <v>-2400000</v>
       </c>
       <c r="M4" t="n">
-        <v>-43500000</v>
+        <v>-48100000</v>
       </c>
       <c r="N4" t="n">
-        <v>-43500000</v>
+        <v>-48100000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3900000</v>
+        <v>-7200000</v>
       </c>
       <c r="P4" t="n">
-        <v>-15700000</v>
+        <v>-11300000</v>
       </c>
       <c r="Q4" t="n">
-        <v>11800000</v>
+        <v>4100000</v>
       </c>
       <c r="R4" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-400000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>8300000</v>
+        <v>-11000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1800000</v>
+        <v>10000000</v>
       </c>
       <c r="Z4" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-12300000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-14300000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>196000000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-25200000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>43200000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>21600000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>116200000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-10800000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-83800000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>13700000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="AO4" t="n">
         <v>1400000</v>
       </c>
-      <c r="AA4" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-9900000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-10500000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>54700000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-20300000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-64500000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-4300000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>71600000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-45400000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-86400000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-19500000</v>
-      </c>
       <c r="AP4" t="n">
-        <v>24900000</v>
+        <v>29700000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2000000</v>
+        <v>2900000</v>
       </c>
       <c r="AR4" t="n">
-        <v>22900000</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>26800000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>400000</v>
+      </c>
       <c r="AT4" t="n">
-        <v>-500000</v>
+        <v>-100000</v>
       </c>
       <c r="AU4" t="n">
-        <v>88300000</v>
+        <v>140600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>102500000</v>
+        <v>110600000</v>
       </c>
       <c r="C5" t="n">
-        <v>-33600000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>-47200000</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2000000</v>
+        <v>29200000</v>
       </c>
       <c r="G5" t="n">
-        <v>-8000000</v>
+        <v>-18200000</v>
       </c>
       <c r="H5" t="n">
-        <v>358400000</v>
+        <v>492400000</v>
       </c>
       <c r="I5" t="n">
-        <v>333200000</v>
+        <v>460700000</v>
       </c>
       <c r="J5" t="n">
-        <v>25200000</v>
+        <v>31700000</v>
       </c>
       <c r="K5" t="n">
-        <v>-80800000</v>
+        <v>-101800000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1700000</v>
+        <v>-1900000</v>
       </c>
       <c r="M5" t="n">
-        <v>-32300000</v>
+        <v>-56100000</v>
       </c>
       <c r="N5" t="n">
-        <v>-32300000</v>
+        <v>-56100000</v>
       </c>
       <c r="O5" t="n">
-        <v>-31600000</v>
+        <v>-18000000</v>
       </c>
       <c r="P5" t="n">
-        <v>-33600000</v>
+        <v>-47200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+        <v>29200000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-4500000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>600000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1300000</v>
-      </c>
       <c r="AC5" t="n">
-        <v>-5300000</v>
+        <v>-16300000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1400000</v>
+        <v>1900000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6700000</v>
+        <v>-18200000</v>
       </c>
       <c r="AF5" t="n">
-        <v>110500000</v>
+        <v>128800000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-28300000</v>
+        <v>-43900000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-52700000</v>
+        <v>-33800000</v>
       </c>
       <c r="AI5" t="n">
-        <v>22900000</v>
+        <v>14600000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>73500000</v>
+        <v>29100000</v>
       </c>
       <c r="AK5" t="n">
-        <v>5700000</v>
+        <v>-131300000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-154800000</v>
+        <v>53800000</v>
       </c>
       <c r="AM5" t="n">
-        <v>4000000</v>
+        <v>2100000</v>
       </c>
       <c r="AN5" t="n">
-        <v>12100000</v>
+        <v>10500000</v>
       </c>
       <c r="AO5" t="n">
-        <v>26400000</v>
+        <v>8700000</v>
       </c>
       <c r="AP5" t="n">
-        <v>22000000</v>
+        <v>33600000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1500000</v>
+        <v>500000</v>
       </c>
       <c r="AR5" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1900000</v>
-      </c>
+        <v>33100000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>-500000</v>
+        <v>-700000</v>
       </c>
       <c r="AU5" t="n">
-        <v>129800000</v>
+        <v>162000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>170700000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-40700000</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-16600000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>531200000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>492400000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38800000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-124300000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-65800000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-65800000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-28200000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-40700000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-24200000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-15500000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>187300000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-48300000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-21000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>209300000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-127300000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-111300000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>36200000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>35800000</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>224900000</v>
       </c>
     </row>
   </sheetData>
@@ -3621,197 +3827,197 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="DR1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -3896,7 +4102,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. John Christopher Morgan', 'age': 70, 'title': 'Founder, CEO &amp; Director', 'yearBorn': 1955, 'fiscalYear': 2025, 'totalPay': 1913360, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kelly  Gangotra', 'title': 'Chief Financial &amp; Commercial Officer and Director', 'fiscalYear': 2025, 'totalPay': 1531150, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lisa Ann Katherine Minns', 'title': 'General Counsel &amp; Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Catherine  Beaumont', 'title': 'Communications Manager', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Camilla  Aitchison', 'age': 65, 'title': 'Director of People', 'yearBorn': 1960, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Pat  Boyle', 'title': 'Managing Director of Morgan Sindall Construction', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chris  Booth', 'title': 'Managing Director of Fit Out', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Martin  Lubieniecki', 'title': 'Managing Director of Design', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Simon  Smith', 'title': 'Managing Director of Infrastructure', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Steve  Coleby', 'title': 'Managing Director of Partnership Housing', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. John Christopher Morgan', 'age': 70, 'title': 'Founder, CEO &amp; Director', 'yearBorn': 1955, 'fiscalYear': 2025, 'totalPay': 1917931, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kelly  Gangotra', 'title': 'Chief Financial &amp; Commercial Officer and Director', 'fiscalYear': 2025, 'totalPay': 1534808, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lisa Ann Katherine Minns', 'title': 'General Counsel &amp; Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Catherine  Beaumont', 'title': 'Communications Manager', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Camilla  Aitchison', 'age': 65, 'title': 'Director of People', 'yearBorn': 1960, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Pat  Boyle', 'title': 'Managing Director of Morgan Sindall Construction', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chris  Booth', 'title': 'Managing Director of Fit Out', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Martin  Lubieniecki', 'title': 'Managing Director of Design', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Simon  Smith', 'title': 'Managing Director of Infrastructure', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Steve  Coleby', 'title': 'Managing Director of Partnership Housing', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3914,34 +4120,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="W2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="X2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.63</v>
+        <v>3.41</v>
       </c>
       <c r="AE2" t="n">
         <v>1778716800</v>
@@ -3953,40 +4159,40 @@
         <v>4.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.849</v>
+        <v>0.851</v>
       </c>
       <c r="AI2" t="n">
-        <v>12.317074</v>
+        <v>13.26034</v>
       </c>
       <c r="AJ2" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="AM2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>51.5</v>
+        <v>54.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>52.5</v>
+        <v>55.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2355997440</v>
+        <v>2542611200</v>
       </c>
       <c r="AR2" t="n">
-        <v>2352019983</v>
+        <v>2556088096</v>
       </c>
       <c r="AS2" t="n">
-        <v>44.4</v>
+        <v>46.6</v>
       </c>
       <c r="AT2" t="n">
         <v>63</v>
@@ -3998,19 +4204,19 @@
         <v>15.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.46945313</v>
+        <v>0.5066376</v>
       </c>
       <c r="AX2" t="n">
-        <v>52.34</v>
+        <v>53.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.288</v>
+        <v>53.546</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.58</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.031600002</v>
+        <v>0.02925926</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -4021,31 +4227,31 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>1898013184</v>
+        <v>2037950592</v>
       </c>
       <c r="BE2" t="n">
         <v>0.034849998</v>
       </c>
       <c r="BF2" t="n">
-        <v>39999711</v>
+        <v>39993180</v>
       </c>
       <c r="BG2" t="n">
         <v>46653414</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.10479</v>
+        <v>0.10496</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.53696</v>
+        <v>0.53566</v>
       </c>
       <c r="BJ2" t="n">
         <v>46653414</v>
       </c>
       <c r="BK2" t="n">
-        <v>18.536612</v>
+        <v>18.606382</v>
       </c>
       <c r="BL2" t="n">
-        <v>2.7243383</v>
+        <v>2.9291024</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4063,19 +4269,19 @@
         <v>174900000</v>
       </c>
       <c r="BR2" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.378</v>
+        <v>0.406</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.118</v>
+        <v>8.717000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.09170306</v>
+        <v>0.08000003999999999</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BW2" t="n">
         <v>1.08</v>
@@ -4089,7 +4295,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>50.5</v>
+        <v>54.5</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4191,146 +4397,146 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Morgan Sindall Group plc</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.9259259</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1781848933</v>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>finmb_875700</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DM2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>dr_market</t>
         </is>
       </c>
-      <c r="DK2" t="b">
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DM2" t="b">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Morgan Sindall Group PLC      R</t>
+        </is>
+      </c>
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Morgan Sindall Group PLC      R</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>1780380366</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Morgan Sindall Group plc</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1612162800000</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>54.5 - 54.5</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>33</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>6.0999985</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.13738735</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>44.4 - 63.0</t>
-        </is>
-      </c>
       <c r="DW2" t="n">
-        <v>-12.5</v>
+        <v>54</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1984127</v>
+        <v>7.9000015</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.170305000000001</v>
-      </c>
-      <c r="DZ2" t="n">
+        <v>0.16952793</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>46.6 - 63.0</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.13492064</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>8.000004000000001</v>
+      </c>
+      <c r="ED2" t="n">
         <v>1772053200</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EE2" t="n">
         <v>1772053200</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="EF2" t="n">
         <v>1772010000</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EG2" t="n">
         <v>1772010000</v>
       </c>
-      <c r="ED2" t="b">
+      <c r="EH2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-1.8400002</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.03515476</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-2.7879982</v>
-      </c>
       <c r="EI2" t="n">
-        <v>-0.05231944</v>
+        <v>4.11</v>
       </c>
       <c r="EJ2" t="n">
+        <v>1.2900009</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0.02424358</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.95399857</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.01781643</v>
+      </c>
+      <c r="EN2" t="n">
         <v>15</v>
       </c>
-      <c r="EK2" t="n">
+      <c r="EO2" t="n">
         <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1612162800000</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>50.5 - 50.5</t>
-        </is>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
